--- a/tests/worked_examples/staged/one_stage_equals_a_plain_evaluation.xlsx
+++ b/tests/worked_examples/staged/one_stage_equals_a_plain_evaluation.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>the staged-evaluator harness (tests/worked_example_runners.py::_staged_values), 2026-09-19</t>
+          <t>the staged-evaluator harness (tests/worked_example_runners.py::_staged_values), 2026-09-20</t>
         </is>
       </c>
     </row>
@@ -498,6 +498,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
@@ -637,6 +638,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
